--- a/public/exports-from-60/11715311.xlsx
+++ b/public/exports-from-60/11715311.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311017829</t>
+          <t xml:space="preserve">311017836</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123153</t>
+          <t xml:space="preserve">311123156</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">

--- a/public/exports-from-60/11715311.xlsx
+++ b/public/exports-from-60/11715311.xlsx
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 30</t>
+          <t xml:space="preserve">Nymøllevej 38</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060987</t>
+          <t xml:space="preserve">2060298</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>360</v>
+        <v>807</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311090351</t>
+          <t xml:space="preserve">311092119</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-09</t>
+          <t xml:space="preserve">2025-01-22</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymøllevej 38</t>
+          <t xml:space="preserve">Rustenborgvej 19A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060298</t>
+          <t xml:space="preserve">8864451</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092119</t>
+          <t xml:space="preserve">311092129</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 19A</t>
+          <t xml:space="preserve">Toftebæksvej 11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864451</t>
+          <t xml:space="preserve">2029421</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>819</v>
+        <v>216</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092129</t>
+          <t xml:space="preserve">311092135</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 11</t>
+          <t xml:space="preserve">Toftebæksvej 38</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029421</t>
+          <t xml:space="preserve">9166452</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>216</v>
+        <v>377</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092135</t>
+          <t xml:space="preserve">311092130</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 38</t>
+          <t xml:space="preserve">Trongårdsvej 58</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9166452</t>
+          <t xml:space="preserve">8864449</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J114">
-        <v>377</v>
+        <v>527</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092130</t>
+          <t xml:space="preserve">311092132</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 58</t>
+          <t xml:space="preserve">Hjortholmsvej 6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,20 +8601,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864449</t>
+          <t xml:space="preserve">2028340</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>527</v>
+        <v>339</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092132</t>
+          <t xml:space="preserve">311095074</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-22</t>
+          <t xml:space="preserve">2025-02-11</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 6</t>
+          <t xml:space="preserve">Kongevejen 49</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028340</t>
+          <t xml:space="preserve">2027995</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>339</v>
+        <v>244</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311095074</t>
+          <t xml:space="preserve">311095076</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,17 +8741,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 49</t>
+          <t xml:space="preserve">Virumgårdsvej 22A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027995</t>
+          <t xml:space="preserve">2103443</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>244</v>
+        <v>690</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311095076</t>
+          <t xml:space="preserve">311096443</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-11</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22A</t>
+          <t xml:space="preserve">Virumgårdsvej 22B</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103443</t>
+          <t xml:space="preserve">8864754</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J118">
-        <v>690</v>
+        <v>712</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096443</t>
+          <t xml:space="preserve">311096444</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22B</t>
+          <t xml:space="preserve">Virumgårdsvej 22C</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8906,15 +8906,15 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J119">
-        <v>712</v>
+        <v>824</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096444</t>
+          <t xml:space="preserve">311096445</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22C</t>
+          <t xml:space="preserve">Virumgårdsvej 2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864754</t>
+          <t xml:space="preserve">2103482</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>824</v>
+        <v>374</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096445</t>
+          <t xml:space="preserve">311098179</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 2</t>
+          <t xml:space="preserve">Virumvej 35</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103482</t>
+          <t xml:space="preserve">8864754</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="J121">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098179</t>
+          <t xml:space="preserve">311098180</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 35</t>
+          <t xml:space="preserve">Jernbanepladsen 22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864754</t>
+          <t xml:space="preserve">2030553</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>350</v>
+        <v>904</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098180</t>
+          <t xml:space="preserve">311104767</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-04-01</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanepladsen 22</t>
+          <t xml:space="preserve">Jernbanevej 16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030553</t>
+          <t xml:space="preserve">2030573</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>904</v>
+        <v>436</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104767</t>
+          <t xml:space="preserve">311104762</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 16</t>
+          <t xml:space="preserve">Rustenborgvej 1C</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030573</t>
+          <t xml:space="preserve">2030225</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104762</t>
+          <t xml:space="preserve">311104760</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J125">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 1C</t>
+          <t xml:space="preserve">Rustenborgvej 2A</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,20 +9426,20 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030225</t>
+          <t xml:space="preserve">2030254</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104760</t>
+          <t xml:space="preserve">311104759</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 2A</t>
+          <t xml:space="preserve">Rustenborgvej 3</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030254</t>
+          <t xml:space="preserve">2030252</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>296</v>
+        <v>444</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104759</t>
+          <t xml:space="preserve">311104755</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 3</t>
+          <t xml:space="preserve">Nørregade 9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,20 +9576,20 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030252</t>
+          <t xml:space="preserve">8864425</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J128">
-        <v>444</v>
+        <v>235</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104755</t>
+          <t xml:space="preserve">311107482</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-01</t>
+          <t xml:space="preserve">2025-04-17</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9656,15 +9656,15 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107482</t>
+          <t xml:space="preserve">311107735</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-17</t>
+          <t xml:space="preserve">2025-04-20</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9731,11 +9731,11 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J130">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 9</t>
+          <t xml:space="preserve">Sorgenfrivej 13</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864425</t>
+          <t xml:space="preserve">2029916</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>224</v>
+        <v>502</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107735</t>
+          <t xml:space="preserve">311107784</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrivej 13</t>
+          <t xml:space="preserve">Nørregade 14</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029916</t>
+          <t xml:space="preserve">8864425</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J132">
-        <v>502</v>
+        <v>202</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107784</t>
+          <t xml:space="preserve">311108491</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-20</t>
+          <t xml:space="preserve">2025-04-23</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9956,11 +9956,11 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J133">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10016,40 +10016,40 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 14</t>
+          <t xml:space="preserve">Taarbæk Strandvej 84</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864425</t>
+          <t xml:space="preserve">2047087</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J134">
-        <v>198</v>
+        <v>545</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311108491</t>
+          <t xml:space="preserve">311123153</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-23</t>
+          <t xml:space="preserve">2025-07-03</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,40 +10091,40 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 84</t>
+          <t xml:space="preserve">Hasselvej 74B</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047087</t>
+          <t xml:space="preserve">1301698</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J135">
-        <v>545</v>
+        <v>298</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123156</t>
+          <t xml:space="preserve">311136466</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-03</t>
+          <t xml:space="preserve">2025-09-24</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10181,15 +10181,15 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J136">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136466</t>
+          <t xml:space="preserve">311136474</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,40 +10241,40 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hasselvej 74B</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301698</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J137">
-        <v>355</v>
+        <v>846</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136474</t>
+          <t xml:space="preserve">311139246</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-24</t>
+          <t xml:space="preserve">2025-10-09</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Lundtoftevej 53C</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,16 +10326,16 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">715219, 8864426</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="J138">
-        <v>846</v>
+        <v>135</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53C</t>
+          <t xml:space="preserve">Buddingevej 39</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,30 +10401,30 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">715219, 8864426</t>
+          <t xml:space="preserve">2064573</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J139">
-        <v>135</v>
+        <v>334</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139246</t>
+          <t xml:space="preserve">311145808</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-09</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,40 +10466,40 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddingevej 39</t>
+          <t xml:space="preserve">Askevænget 10</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064573</t>
+          <t xml:space="preserve">1301698</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J140">
-        <v>334</v>
+        <v>1060</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145808</t>
+          <t xml:space="preserve">311150499</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2025-12-16</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,30 +10541,30 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askevænget 10</t>
+          <t xml:space="preserve">Nøjsomhedsvej 11</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301698</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J141">
-        <v>1060</v>
+        <v>634</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311150499</t>
+          <t xml:space="preserve">311176540</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-16</t>
+          <t xml:space="preserve">2026-05-13</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 11</t>
+          <t xml:space="preserve">Lyngby Torv 16</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2030182</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>634</v>
+        <v>266</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176540</t>
+          <t xml:space="preserve">311179524</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-13</t>
+          <t xml:space="preserve">2026-05-30</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Torv 16</t>
+          <t xml:space="preserve">Hjortholmsvej 3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030182</t>
+          <t xml:space="preserve">2028337</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179524</t>
+          <t xml:space="preserve">311195275</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-30</t>
+          <t xml:space="preserve">2026-08-18</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 3</t>
+          <t xml:space="preserve">Kongsvænget 10C</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028337</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J144">
-        <v>356</v>
+        <v>853</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311195275</t>
+          <t xml:space="preserve">311196141</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-18</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10C</t>
+          <t xml:space="preserve">Grønnevej 218</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,20 +10851,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2103430</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J145">
-        <v>853</v>
+        <v>813</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196141</t>
+          <t xml:space="preserve">311198636</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10911,55 +10911,55 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">173</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 218</t>
+          <t xml:space="preserve">Lejrvej 47</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103430</t>
+          <t xml:space="preserve">2134936</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>813</v>
+        <v>636</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198636</t>
+          <t xml:space="preserve">311231307</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10986,45 +10986,45 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">173</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvej 47</t>
+          <t xml:space="preserve">Christian X's Alle 95C</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134936</t>
+          <t xml:space="preserve">206570</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J147">
-        <v>636</v>
+        <v>300</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231307</t>
+          <t xml:space="preserve">311230119</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95C</t>
+          <t xml:space="preserve">Christian X's Alle 95D</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J148">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230119</t>
+          <t xml:space="preserve">311230118</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95D</t>
+          <t xml:space="preserve">Christian X's Alle 95E</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11156,15 +11156,15 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J149">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230118</t>
+          <t xml:space="preserve">311230107</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,40 +11216,40 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95E</t>
+          <t xml:space="preserve">Strandvejen 607</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">206570</t>
+          <t xml:space="preserve">2047266</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>450</v>
+        <v>148</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230107</t>
+          <t xml:space="preserve">311233876</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
+          <t xml:space="preserve">Møllevang Tegnestue</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,40 +11291,40 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 607</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047266</t>
+          <t xml:space="preserve">1301455</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J151">
-        <v>148</v>
+        <v>1774</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233876</t>
+          <t xml:space="preserve">311245601</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevang Tegnestue</t>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301455</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>1774</v>
+        <v>680</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245601</t>
+          <t xml:space="preserve">311245596</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11456,15 +11456,15 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J153">
-        <v>680</v>
+        <v>1946</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245596</t>
+          <t xml:space="preserve">311245602</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Toftebæksvej 8</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">8864411</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>1946</v>
+        <v>942</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245602</t>
+          <t xml:space="preserve">311251199</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-05</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 8</t>
+          <t xml:space="preserve">Ravnholmvej 7</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864411</t>
+          <t xml:space="preserve">2062047</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>942</v>
+        <v>266</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251199</t>
+          <t xml:space="preserve">311290836</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnholmvej 7</t>
+          <t xml:space="preserve">Taarbæk Strandvej 90</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062047</t>
+          <t xml:space="preserve">2047232</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290836</t>
+          <t xml:space="preserve">311290924</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-02</t>
+          <t xml:space="preserve">2028-01-03</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 90</t>
+          <t xml:space="preserve">Caroline Amalie Vej 118</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047232</t>
+          <t xml:space="preserve">8864558</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>295</v>
+        <v>864</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290924</t>
+          <t xml:space="preserve">311295408</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-03</t>
+          <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 118</t>
+          <t xml:space="preserve">Caroline Amalie Vej 120</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J158">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295408</t>
+          <t xml:space="preserve">311295440</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 120</t>
+          <t xml:space="preserve">Caroline Amalie Vej 122</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11906,15 +11906,15 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J159">
-        <v>864</v>
+        <v>969</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295440</t>
+          <t xml:space="preserve">311295444</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 122</t>
+          <t xml:space="preserve">Caroline Amalie Vej 124</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11981,15 +11981,15 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J160">
-        <v>969</v>
+        <v>658</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295444</t>
+          <t xml:space="preserve">311295460</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 124</t>
+          <t xml:space="preserve">Caroline Amalie Vej 126</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12056,15 +12056,15 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J161">
-        <v>658</v>
+        <v>3833</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295460</t>
+          <t xml:space="preserve">311295495</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 126</t>
+          <t xml:space="preserve">Jægersborgvej 19</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,20 +12126,20 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864558</t>
+          <t xml:space="preserve">2028514</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>3833</v>
+        <v>232</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295495</t>
+          <t xml:space="preserve">311297484</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-31</t>
+          <t xml:space="preserve">2028-02-13</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborgvej 19</t>
+          <t xml:space="preserve">Lyngby Hovedgade 102A</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028514</t>
+          <t xml:space="preserve">2065603</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>232</v>
+        <v>2277</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311297484</t>
+          <t xml:space="preserve">311298110</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-13</t>
+          <t xml:space="preserve">2028-02-16</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 102A</t>
+          <t xml:space="preserve">Christian X's Alle 97A</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065603</t>
+          <t xml:space="preserve">100497999</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J164">
-        <v>2277</v>
+        <v>280</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298110</t>
+          <t xml:space="preserve">311306901</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-16</t>
+          <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 97A</t>
+          <t xml:space="preserve">Sorgenfrigårdsvej 37</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100497999</t>
+          <t xml:space="preserve">2029392</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306901</t>
+          <t xml:space="preserve">311313170</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-06</t>
+          <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrigårdsvej 37</t>
+          <t xml:space="preserve">Fuglevadsvej 49</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029392</t>
+          <t xml:space="preserve">1300682</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>317</v>
+        <v>1035</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313170</t>
+          <t xml:space="preserve">311315069</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-09</t>
+          <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevadsvej 49</t>
+          <t xml:space="preserve">Lundtofte Skolestr. 7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300682</t>
+          <t xml:space="preserve">2060774</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J167">
-        <v>1035</v>
+        <v>148</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315069</t>
+          <t xml:space="preserve">311317367</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-18</t>
+          <t xml:space="preserve">2028-05-30</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtofte Skolestr. 7</t>
+          <t xml:space="preserve">Ravnholmvej 11</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12581,11 +12581,11 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>148</v>
+        <v>2508</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnholmvej 11</t>
+          <t xml:space="preserve">Kulsviervej 5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,30 +12651,30 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060774</t>
+          <t xml:space="preserve">2062257</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>2508</v>
+        <v>264</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317367</t>
+          <t xml:space="preserve">311319303</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-30</t>
+          <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 5</t>
+          <t xml:space="preserve">Toftebæksvej 17</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,25 +12726,25 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062257</t>
+          <t xml:space="preserve">8864437</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>264</v>
+        <v>850</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319303</t>
+          <t xml:space="preserve">311319296</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -12791,17 +12791,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 17</t>
+          <t xml:space="preserve">Grønnevej 218</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864437</t>
+          <t xml:space="preserve">2103430</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,11 +12810,11 @@
         </is>
       </c>
       <c r="J171">
-        <v>850</v>
+        <v>3585</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319296</t>
+          <t xml:space="preserve">311324386</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-08</t>
+          <t xml:space="preserve">2028-07-03</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12881,15 +12881,15 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J172">
-        <v>3585</v>
+        <v>640</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324386</t>
+          <t xml:space="preserve">311324387</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12956,15 +12956,15 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J173">
-        <v>640</v>
+        <v>1326</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324387</t>
+          <t xml:space="preserve">311324386</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 218</t>
+          <t xml:space="preserve">Geels Plads 40</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,20 +13026,20 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103430</t>
+          <t xml:space="preserve">2074600</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J174">
-        <v>1326</v>
+        <v>3579</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324386</t>
+          <t xml:space="preserve">311330677</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-03</t>
+          <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geels Plads 40</t>
+          <t xml:space="preserve">Trongårdsvej 50</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2074600</t>
+          <t xml:space="preserve">8864449</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J175">
-        <v>3579</v>
+        <v>986</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330677</t>
+          <t xml:space="preserve">311330689</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 50</t>
+          <t xml:space="preserve">Trongårdsvej 60</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13181,15 +13181,15 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J176">
-        <v>986</v>
+        <v>130</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330689</t>
+          <t xml:space="preserve">311330692</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 60</t>
+          <t xml:space="preserve">Trongårdsvej 50</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13256,15 +13256,15 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>130</v>
+        <v>6598</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330692</t>
+          <t xml:space="preserve">311331058</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-15</t>
+          <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 50</t>
+          <t xml:space="preserve">Kongevejen 55</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864449</t>
+          <t xml:space="preserve">2028010</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J178">
-        <v>6598</v>
+        <v>1575</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311331058</t>
+          <t xml:space="preserve">311333738</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-17</t>
+          <t xml:space="preserve">2028-08-31</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13406,11 +13406,11 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J179">
-        <v>1575</v>
+        <v>370</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 55</t>
+          <t xml:space="preserve">Kongevejen 57</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J180">
-        <v>370</v>
+        <v>535</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 57</t>
+          <t xml:space="preserve">Lyngbygårdsvej 37</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028010</t>
+          <t xml:space="preserve">2029334</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,21 +13560,21 @@
         </is>
       </c>
       <c r="J181">
-        <v>535</v>
+        <v>6394</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311333738</t>
+          <t xml:space="preserve">311336039</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-31</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13631,11 +13631,11 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J182">
-        <v>6394</v>
+        <v>503</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13706,20 +13706,20 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J183">
-        <v>503</v>
+        <v>205</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336039</t>
+          <t xml:space="preserve">311336048</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbygårdsvej 37</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029334</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336048</t>
+          <t xml:space="preserve">311336291</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-14</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Kongsvænget 10B</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J185">
-        <v>3540</v>
+        <v>2552</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13916,30 +13916,30 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Lyngby Hovedgade 28</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2030466</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>428</v>
+        <v>4499</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311337951</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,40 +13991,40 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Nybrovej 401B</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">8864737</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J187">
-        <v>431</v>
+        <v>497</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311339703</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-10-04</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,17 +14066,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Nybrovej 401C</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">8864737</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,21 +14085,21 @@
         </is>
       </c>
       <c r="J188">
-        <v>235</v>
+        <v>100</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336291</t>
+          <t xml:space="preserve">311339704</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-10-04</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,40 +14141,40 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10B</t>
+          <t xml:space="preserve">Becksvej 3</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2047221</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J189">
-        <v>2552</v>
+        <v>327</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311345047</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 28</t>
+          <t xml:space="preserve">Lyngby Hovedgade 1A</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030466</t>
+          <t xml:space="preserve">203119</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,21 +14235,21 @@
         </is>
       </c>
       <c r="J190">
-        <v>4499</v>
+        <v>3922</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337951</t>
+          <t xml:space="preserve">311345064</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-25</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,30 +14291,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 401B</t>
+          <t xml:space="preserve">Taarbæk Strandvej 96A</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864737</t>
+          <t xml:space="preserve">2047221</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>497</v>
+        <v>2624</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339703</t>
+          <t xml:space="preserve">311345057</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-04</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 401C</t>
+          <t xml:space="preserve">Bauneporten 20</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,20 +14376,20 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864737</t>
+          <t xml:space="preserve">2029353</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>100</v>
+        <v>3101</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339704</t>
+          <t xml:space="preserve">311346074</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-04</t>
+          <t xml:space="preserve">2028-11-09</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Becksvej 3</t>
+          <t xml:space="preserve">Parcelvej 151</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047221</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,21 +14460,21 @@
         </is>
       </c>
       <c r="J193">
-        <v>327</v>
+        <v>136</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345047</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,40 +14516,40 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 1A</t>
+          <t xml:space="preserve">Parcelvej 151</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">203119</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J194">
-        <v>3922</v>
+        <v>160</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345064</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 96A</t>
+          <t xml:space="preserve">Parcelvej 153</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047221</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,21 +14610,21 @@
         </is>
       </c>
       <c r="J195">
-        <v>2624</v>
+        <v>148</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345057</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,40 +14666,40 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bauneporten 20</t>
+          <t xml:space="preserve">Skolebakken 9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029353</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J196">
-        <v>3101</v>
+        <v>16483</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346074</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-09</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,40 +14741,40 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 151</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>136</v>
+        <v>4637</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,40 +14816,40 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 151</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J198">
-        <v>160</v>
+        <v>3693</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,40 +14891,40 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 153</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J199">
-        <v>148</v>
+        <v>1405</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,40 +14966,40 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 9</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J200">
-        <v>16483</v>
+        <v>3674</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Gyrithe Lemches Vej 14</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15056,15 +15056,15 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J201">
-        <v>4637</v>
+        <v>908</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311362217</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-01</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Christian X's Alle 95A</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,20 +15126,20 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">206570</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J202">
-        <v>3693</v>
+        <v>1790</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311367421</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-27</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Christian X's Alle 95B</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15201,20 +15201,20 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">206568, 206569</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J203">
-        <v>1405</v>
+        <v>782</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311367239</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-27</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Biskop Monrads Vej 15</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">2102160</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J204">
-        <v>3674</v>
+        <v>164</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311481405</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyrithe Lemches Vej 14</t>
+          <t xml:space="preserve">Christian X's Alle 113</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,30 +15351,30 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">1301456</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J205">
-        <v>908</v>
+        <v>266</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311362217</t>
+          <t xml:space="preserve">311481297</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-01</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95A</t>
+          <t xml:space="preserve">Gasværksvej 10</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">206570</t>
+          <t xml:space="preserve">2028305</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15435,11 +15435,11 @@
         </is>
       </c>
       <c r="J206">
-        <v>1790</v>
+        <v>194</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367421</t>
+          <t xml:space="preserve">311481418</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-27</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95B</t>
+          <t xml:space="preserve">Kulsviervej 115</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,20 +15501,20 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">206568, 206569</t>
+          <t xml:space="preserve">2060251</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>782</v>
+        <v>470</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367239</t>
+          <t xml:space="preserve">311481296</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-27</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,30 +15566,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biskop Monrads Vej 15</t>
+          <t xml:space="preserve">Lundtoftevej 212</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102160</t>
+          <t xml:space="preserve">2061449</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481405</t>
+          <t xml:space="preserve">311481407</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 113</t>
+          <t xml:space="preserve">Lundtoftevej 218</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301456</t>
+          <t xml:space="preserve">8864537</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,16 +15660,16 @@
         </is>
       </c>
       <c r="J209">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481297</t>
+          <t xml:space="preserve">311481412</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 10</t>
+          <t xml:space="preserve">Lyngby Hovedgade 70C</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028305</t>
+          <t xml:space="preserve">100052, 100053, 100054, 100055</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,11 +15735,11 @@
         </is>
       </c>
       <c r="J210">
-        <v>194</v>
+        <v>432</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481418</t>
+          <t xml:space="preserve">311481300</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 115</t>
+          <t xml:space="preserve">Nybrovej 457</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060251</t>
+          <t xml:space="preserve">2102136</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>470</v>
+        <v>185</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481296</t>
+          <t xml:space="preserve">311481385</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 212</t>
+          <t xml:space="preserve">Virumvej 121</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061449</t>
+          <t xml:space="preserve">2077301</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,11 +15885,11 @@
         </is>
       </c>
       <c r="J212">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481407</t>
+          <t xml:space="preserve">311481298</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 218</t>
+          <t xml:space="preserve">Lottenborgvej 16</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864537</t>
+          <t xml:space="preserve">2028027</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="J213">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481412</t>
+          <t xml:space="preserve">311484955</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 70C</t>
+          <t xml:space="preserve">Lottenborgvej 16</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052, 100053, 100054, 100055</t>
+          <t xml:space="preserve">2028027</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J214">
-        <v>432</v>
+        <v>121</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481300</t>
+          <t xml:space="preserve">311484954</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 457</t>
+          <t xml:space="preserve">Lundtoftevej 51A</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102136</t>
+          <t xml:space="preserve">2029203</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481385</t>
+          <t xml:space="preserve">311485502</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,17 +16166,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 121</t>
+          <t xml:space="preserve">Lundtoftevej 55A</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077301</t>
+          <t xml:space="preserve">2029204</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,11 +16185,11 @@
         </is>
       </c>
       <c r="J216">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481298</t>
+          <t xml:space="preserve">311485503</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lottenborgvej 16</t>
+          <t xml:space="preserve">Lundtoftevej 57A</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028027</t>
+          <t xml:space="preserve">2029205</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -16260,11 +16260,11 @@
         </is>
       </c>
       <c r="J217">
-        <v>91</v>
+        <v>214</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484955</t>
+          <t xml:space="preserve">311485504</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lottenborgvej 16</t>
+          <t xml:space="preserve">Lundtoftevej 59A</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,20 +16326,20 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028027</t>
+          <t xml:space="preserve">2029206</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J218">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484954</t>
+          <t xml:space="preserve">311485505</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2031-01-04</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 51A</t>
+          <t xml:space="preserve">Gammel Lundtoftevej 6</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029203</t>
+          <t xml:space="preserve">2030472</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485502</t>
+          <t xml:space="preserve">311520616</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 55A</t>
+          <t xml:space="preserve">Lyngby Hovedgade 1C</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029204</t>
+          <t xml:space="preserve">100052706</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,11 +16485,11 @@
         </is>
       </c>
       <c r="J220">
-        <v>216</v>
+        <v>591</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485503</t>
+          <t xml:space="preserve">311520638</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 57A</t>
+          <t xml:space="preserve">Åstræde 1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029205</t>
+          <t xml:space="preserve">8864464</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>214</v>
+        <v>913</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485504</t>
+          <t xml:space="preserve">311520617</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 59A</t>
+          <t xml:space="preserve">Rævehøjparken 1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029206</t>
+          <t xml:space="preserve">212522, 100645398, 100645399, 100645400, 100645401, 100645402, 100645403, 100645404, 100645405, 100645406, 100645407, 100645408, 100645409, 100645410, 100645411, 100645412, 100645413, 100645414, 100645415, 100645416, 100645417, 100645418, 100645419, 100645420, 100645421, 100645422, 100645423, 100645424, 100645425, 100645426, 100645427</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="J222">
-        <v>214</v>
+        <v>1848</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485505</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-04</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Lundtoftevej 6</t>
+          <t xml:space="preserve">Rævehøjparken 11</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,30 +16701,30 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030472</t>
+          <t xml:space="preserve">100645428, 100645429, 100645430, 100645431, 100645432, 100645433, 100645434, 100645435, 100645436, 100645437, 100645438, 100645439, 100645440, 100645441, 100645442, 100645443, 100645444, 100645445, 100645446, 100645447, 100645448, 100645449, 100645450, 100645451, 100645452, 100645453, 100645454, 100645455, 100645456, 100645457</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J223">
-        <v>84</v>
+        <v>1848</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520616</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 1C</t>
+          <t xml:space="preserve">Rævehøjparken 2</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,30 +16776,30 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052706</t>
+          <t xml:space="preserve">100645397, 100645461, 100645462, 100645464, 100645465, 100645466, 100645469, 100645471, 100645473, 100645474, 100645475, 100645476, 100645477, 100645479, 100645481, 100645482, 100645483, 100645484, 100645485, 100645487, 100645458, 100645459, 100645460, 100645463, 100645467, 100645468, 100645470, 100645472, 100645478, 100645480, 100645486</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J224">
-        <v>591</v>
+        <v>1850</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520638</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åstræde 1</t>
+          <t xml:space="preserve">Høstvej 12</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864464</t>
+          <t xml:space="preserve">2029365</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16860,21 +16860,21 @@
         </is>
       </c>
       <c r="J225">
-        <v>913</v>
+        <v>386</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520617</t>
+          <t xml:space="preserve">311569627</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 1</t>
+          <t xml:space="preserve">Høstvej 14</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,30 +16926,30 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">212522, 100645398, 100645399, 100645400, 100645401, 100645402, 100645403, 100645404, 100645405, 100645406, 100645407, 100645408, 100645409, 100645410, 100645411, 100645412, 100645413, 100645414, 100645415, 100645416, 100645417, 100645418, 100645419, 100645420, 100645421, 100645422, 100645423, 100645424, 100645425, 100645426, 100645427</t>
+          <t xml:space="preserve">2029365</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J226">
-        <v>1848</v>
+        <v>566</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311569627</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 11</t>
+          <t xml:space="preserve">Asylgade 9A</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">100645428, 100645429, 100645430, 100645431, 100645432, 100645433, 100645434, 100645435, 100645436, 100645437, 100645438, 100645439, 100645440, 100645441, 100645442, 100645443, 100645444, 100645445, 100645446, 100645447, 100645448, 100645449, 100645450, 100645451, 100645452, 100645453, 100645454, 100645455, 100645456, 100645457</t>
+          <t xml:space="preserve">1300767</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>1848</v>
+        <v>940</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311609045</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 2</t>
+          <t xml:space="preserve">Emil Pipers Vej 5</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17076,30 +17076,30 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">100645397, 100645461, 100645462, 100645464, 100645465, 100645466, 100645469, 100645471, 100645473, 100645474, 100645475, 100645476, 100645477, 100645479, 100645481, 100645482, 100645483, 100645484, 100645485, 100645487, 100645458, 100645459, 100645460, 100645463, 100645467, 100645468, 100645470, 100645472, 100645478, 100645480, 100645486</t>
+          <t xml:space="preserve">2064737</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J228">
-        <v>1850</v>
+        <v>1173</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311609052</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høstvej 12</t>
+          <t xml:space="preserve">Baunehøjvej 6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029365</t>
+          <t xml:space="preserve">2029257</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,21 +17160,21 @@
         </is>
       </c>
       <c r="J229">
-        <v>386</v>
+        <v>1110</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569627</t>
+          <t xml:space="preserve">311614560</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høstvej 14</t>
+          <t xml:space="preserve">Carlshøjvej 7</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17226,30 +17226,30 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029365</t>
+          <t xml:space="preserve">2029261</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J230">
-        <v>566</v>
+        <v>1908</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569627</t>
+          <t xml:space="preserve">311614576</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 9A</t>
+          <t xml:space="preserve">Kastanievej 4A</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300767</t>
+          <t xml:space="preserve">2030205</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,11 +17310,11 @@
         </is>
       </c>
       <c r="J231">
-        <v>940</v>
+        <v>1512</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609045</t>
+          <t xml:space="preserve">311614565</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Pipers Vej 5</t>
+          <t xml:space="preserve">Melagervej 1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064737</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,11 +17385,11 @@
         </is>
       </c>
       <c r="J232">
-        <v>1173</v>
+        <v>328</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609052</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 6</t>
+          <t xml:space="preserve">Melagervej 13</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,20 +17451,20 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029257</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J233">
-        <v>1110</v>
+        <v>656</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614560</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlshøjvej 7</t>
+          <t xml:space="preserve">Melagervej 21</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,20 +17526,20 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029261</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J234">
-        <v>1908</v>
+        <v>656</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614576</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 4A</t>
+          <t xml:space="preserve">Melagervej 5</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,20 +17601,20 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030205</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J235">
-        <v>1512</v>
+        <v>656</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614565</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 1</t>
+          <t xml:space="preserve">Rønne Alle 2</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">2063646</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -17685,11 +17685,11 @@
         </is>
       </c>
       <c r="J236">
-        <v>328</v>
+        <v>1968</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311614558</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 13</t>
+          <t xml:space="preserve">Furesøvej 161</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">1301632</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311618189</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-08-02</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,30 +17816,30 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 21</t>
+          <t xml:space="preserve">Furesøvej 163</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">1301632</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J238">
-        <v>656</v>
+        <v>291</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311618186</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-08-02</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 5</t>
+          <t xml:space="preserve">Lyngby Kirkestræde 8B</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,20 +17901,20 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">2030014</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>656</v>
+        <v>448</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311628911</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønne Alle 2</t>
+          <t xml:space="preserve">Hjortholmsvej 7</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2063646</t>
+          <t xml:space="preserve">2028658</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,21 +17985,21 @@
         </is>
       </c>
       <c r="J240">
-        <v>1968</v>
+        <v>306</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614558</t>
+          <t xml:space="preserve">311646859</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">TT-Energioptimering</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,40 +18041,40 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furesøvej 161</t>
+          <t xml:space="preserve">Fuglevadsvej 47</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301632</t>
+          <t xml:space="preserve">1300682</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J241">
-        <v>552</v>
+        <v>66</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618189</t>
+          <t xml:space="preserve">311657990</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-02</t>
+          <t xml:space="preserve">2033-02-03</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,40 +18116,40 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furesøvej 163</t>
+          <t xml:space="preserve">Firskovvej 41</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301632</t>
+          <t xml:space="preserve">10180201</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>291</v>
+        <v>1556</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618186</t>
+          <t xml:space="preserve">311665365</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-02</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Kirkestræde 8B</t>
+          <t xml:space="preserve">Slotsvænget 23A</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030014</t>
+          <t xml:space="preserve">8864457</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -18210,21 +18210,21 @@
         </is>
       </c>
       <c r="J243">
-        <v>448</v>
+        <v>1832</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311628911</t>
+          <t xml:space="preserve">311665366</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,17 +18266,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 7</t>
+          <t xml:space="preserve">Grønnevej 248</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028658</t>
+          <t xml:space="preserve">2103431</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -18285,21 +18285,21 @@
         </is>
       </c>
       <c r="J244">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646859</t>
+          <t xml:space="preserve">311665965</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">TT-Energioptimering</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevadsvej 47</t>
+          <t xml:space="preserve">Sorgenfrivej 21</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,30 +18351,30 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300682</t>
+          <t xml:space="preserve">2029965</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>66</v>
+        <v>260</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657990</t>
+          <t xml:space="preserve">311665962</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-03</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Firskovvej 41</t>
+          <t xml:space="preserve">Eremitageparken 325</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,30 +18426,30 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180201</t>
+          <t xml:space="preserve">211671, 212016, 212017, 212018, 212019, 212020, 212021, 212022, 212023, 212024, 212025, 212027, 212028, 212029, 212030, 212031, 212032, 212033, 212034, 212035, 212036, 212039, 212038, 212040</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J246">
-        <v>1556</v>
+        <v>1476</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665365</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsvænget 23A</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,30 +18501,30 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864457</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J247">
-        <v>1832</v>
+        <v>623</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665366</t>
+          <t xml:space="preserve">311725677</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,17 +18566,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 248</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103431</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,21 +18585,21 @@
         </is>
       </c>
       <c r="J248">
-        <v>138</v>
+        <v>3933</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665965</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrivej 21</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,30 +18651,30 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029965</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J249">
-        <v>260</v>
+        <v>1086</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665962</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 325</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18726,30 +18726,30 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">211671, 212016, 212017, 212018, 212019, 212020, 212021, 212022, 212023, 212024, 212025, 212027, 212028, 212029, 212030, 212031, 212032, 212033, 212034, 212035, 212036, 212039, 212038, 212040</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J250">
-        <v>1476</v>
+        <v>935</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Toftebæksvej 3A</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,30 +18801,30 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">1300781</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>623</v>
+        <v>480</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725677</t>
+          <t xml:space="preserve">311811264</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve">Fried-Energi ApS</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2035-02-12</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Klintevej 14</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18876,30 +18876,30 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2065128</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J252">
-        <v>3933</v>
+        <v>372</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311824399</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Nøjsomhedsvej 6</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18951,30 +18951,30 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2060670</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>1086</v>
+        <v>119</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311830616</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Nøjsomhedsvej 6</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19026,30 +19026,30 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2060670</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J254">
-        <v>935</v>
+        <v>172</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311830616</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 3A</t>
+          <t xml:space="preserve">Christian X's Alle 117</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,30 +19101,30 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300781</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J255">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311811264</t>
+          <t xml:space="preserve">311862495</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fried-Energi ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-12</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintevej 14</t>
+          <t xml:space="preserve">Christian X's Alle 117</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,30 +19176,30 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065128</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J256">
-        <v>372</v>
+        <v>705</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824399</t>
+          <t xml:space="preserve">311862485</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 6</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,20 +19251,20 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060670</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J257">
-        <v>119</v>
+        <v>1047</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830616</t>
+          <t xml:space="preserve">311862497</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-09</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 6</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,20 +19326,20 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060670</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J258">
-        <v>172</v>
+        <v>1054</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830616</t>
+          <t xml:space="preserve">311862490</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-09</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 117</t>
+          <t xml:space="preserve">Gammel Bagsværdvej 41</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19406,15 +19406,15 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J259">
-        <v>560</v>
+        <v>257</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862495</t>
+          <t xml:space="preserve">311862494</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 117</t>
+          <t xml:space="preserve">Kongevejen 51</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,30 +19476,30 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2027998</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>705</v>
+        <v>366</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862485</t>
+          <t xml:space="preserve">311907609</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">B.F. Byggeservice ApS</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,40 +19541,40 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J261">
-        <v>1047</v>
+        <v>3540</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862497</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,40 +19616,40 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J262">
-        <v>1054</v>
+        <v>428</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862490</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,40 +19691,40 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Bagsværdvej 41</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J263">
-        <v>257</v>
+        <v>431</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862494</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 51</t>
+          <t xml:space="preserve">Nøjsomhedsvej 30</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027998</t>
+          <t xml:space="preserve">2060987</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -19785,21 +19785,21 @@
         </is>
       </c>
       <c r="J264">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907609</t>
+          <t xml:space="preserve">311926684</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.F. Byggeservice ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">

--- a/public/exports-from-60/11715311.xlsx
+++ b/public/exports-from-60/11715311.xlsx
@@ -5014,7 +5014,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311017836</t>
+          <t xml:space="preserve">311017829</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
